--- a/05 Others/2026.1 Avaliação Projetos/Turma Python IoT - ARA0058 Turma 3002 SEMI Wyden UniRuy 2026_1.xlsx
+++ b/05 Others/2026.1 Avaliação Projetos/Turma Python IoT - ARA0058 Turma 3002 SEMI Wyden UniRuy 2026_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YduqsArea1\Avaliações Yduqs 2022_2 BDQ 2023_1 2024_2\2026.1 Avaliação Projetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F443FD-D612-429B-949F-706B8A1D7265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7050B3B0-B4DB-45EA-ACFA-49768D2E6D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DD6ED3E7-57DF-4A52-9E4C-63B0F7661B3D}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
-  <si>
-    <t>-</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
   <si>
     <t>Falta</t>
   </si>
@@ -93,13 +90,34 @@
   </si>
   <si>
     <t>Carla Patricia dos Santos Cantuaris Neves - IES não enxergo Polo UniRuy</t>
+  </si>
+  <si>
+    <t>EQ</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>https://github.com/Luscas8/SimonCognitivo</t>
+  </si>
+  <si>
+    <t>https://github.com/Gograss/monitoramento-vibracao-iot</t>
+  </si>
+  <si>
+    <t>https://github.com/CaueKonceRamos/IoT-Vision-3D</t>
+  </si>
+  <si>
+    <t>https://github.com/HenriqueJanser/SistemadeIrrigacao-TinkerCad</t>
+  </si>
+  <si>
+    <t>não GitHub</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,8 +144,22 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -140,8 +172,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -332,13 +370,131 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -350,35 +506,79 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -711,205 +911,324 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0212B8F-44EC-4B38-84EB-21D2846DA7CB}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="84.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="63.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="20">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="E2" s="6">
+        <v>10</v>
+      </c>
+      <c r="F2" s="6">
+        <f>E2</f>
+        <v>10</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="21">
+        <v>1</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="E3" s="8">
+        <v>10</v>
+      </c>
+      <c r="F3" s="8">
+        <f>E3</f>
+        <v>10</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="12">
+        <v>15</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="E4" s="8">
+        <v>10</v>
+      </c>
+      <c r="F4" s="8">
+        <f t="shared" ref="F4:F8" si="0">E4</f>
+        <v>10</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="12">
+        <v>11</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E5" s="8">
+        <v>9</v>
+      </c>
+      <c r="F5" s="8">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="21">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="C6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8">
+        <v>10</v>
+      </c>
+      <c r="F6" s="8">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="21">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="E7" s="8">
+        <v>10</v>
+      </c>
+      <c r="F7" s="8">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12">
+        <v>15</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="E8" s="8">
+        <v>10</v>
+      </c>
+      <c r="F8" s="8">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="22">
+        <v>7</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="F9" s="10">
+        <f>E9</f>
+        <v>8.5</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="4" t="s">
+    </row>
+    <row r="12" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="14" t="s">
         <v>5</v>
       </c>
+      <c r="G12" s="15" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="1"/>
+    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="16">
+        <v>20</v>
+      </c>
+      <c r="C13" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="D13" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="E13" s="17">
+        <v>7</v>
+      </c>
+      <c r="F13" s="17">
+        <f>E13</f>
+        <v>7</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="9">
-        <v>0.8</v>
-      </c>
-      <c r="C3" s="9">
-        <v>0.3</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="9">
-        <v>0.9</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="9">
-        <v>0.9</v>
-      </c>
-      <c r="C5" s="9">
-        <v>0.4</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="C7" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="18">
         <v>15</v>
       </c>
-      <c r="B8" s="9">
-        <v>1</v>
-      </c>
-      <c r="C8" s="9">
-        <v>0.8</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="12">
-        <v>0.6</v>
-      </c>
-      <c r="C9" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>18</v>
+      <c r="C14" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="19">
+        <v>10</v>
+      </c>
+      <c r="F14" s="19">
+        <f>E14</f>
+        <v>10</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G9" r:id="rId1" xr:uid="{AC5DFFD2-B327-43BA-8780-C2851736B4D2}"/>
+    <hyperlink ref="G6" r:id="rId2" xr:uid="{7D65FF44-E0AE-4BD1-91EE-34BE865B019C}"/>
+    <hyperlink ref="G2" r:id="rId3" xr:uid="{6BDE6611-1995-438D-A92D-E7660BCA162A}"/>
+    <hyperlink ref="G3" r:id="rId4" xr:uid="{FE861FB6-CE4C-4267-BA9C-D016507B0340}"/>
+    <hyperlink ref="G7" r:id="rId5" xr:uid="{F032DE1B-7459-43A1-ADEB-BD545B2706E7}"/>
+    <hyperlink ref="G8" r:id="rId6" xr:uid="{0F8AFA2A-F6E7-43FB-9F99-8C28EC6BBBCC}"/>
+    <hyperlink ref="G4" r:id="rId7" xr:uid="{F26C61E3-1B2A-4283-B2FC-A19D7C6BECA5}"/>
+    <hyperlink ref="G14" r:id="rId8" xr:uid="{DB4137B9-759A-4D22-913C-D16C5B998FCB}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/05 Others/2026.1 Avaliação Projetos/Turma Python IoT - ARA0058 Turma 3002 SEMI Wyden UniRuy 2026_1.xlsx
+++ b/05 Others/2026.1 Avaliação Projetos/Turma Python IoT - ARA0058 Turma 3002 SEMI Wyden UniRuy 2026_1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YduqsArea1\Avaliações Yduqs 2022_2 BDQ 2023_1 2024_2\2026.1 Avaliação Projetos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YduqsArea1\Avaliações Yduqs 2022_2 BDQ 2023_1 2024_2\2026.1 Avaliação Projetos\ok\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7050B3B0-B4DB-45EA-ACFA-49768D2E6D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C271F07-2F3F-4904-B3EE-BE72E381B455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DD6ED3E7-57DF-4A52-9E4C-63B0F7661B3D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="28">
   <si>
     <t>Falta</t>
   </si>
@@ -111,13 +111,22 @@
   </si>
   <si>
     <t>não GitHub</t>
+  </si>
+  <si>
+    <t>ainda não apresentou</t>
+  </si>
+  <si>
+    <t>não GitHub/SAVA</t>
+  </si>
+  <si>
+    <t>apresentou</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,6 +167,19 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -174,7 +196,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -492,7 +514,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -539,9 +561,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -551,15 +570,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -576,6 +586,23 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -920,6 +947,7 @@
     <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -949,7 +977,7 @@
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="29">
         <v>1</v>
       </c>
       <c r="C2" s="6">
@@ -965,7 +993,7 @@
         <f>E2</f>
         <v>10</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="21" t="s">
         <v>22</v>
       </c>
       <c r="H2" s="1"/>
@@ -974,7 +1002,7 @@
       <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="12">
         <v>1</v>
       </c>
       <c r="C3" s="8">
@@ -990,7 +1018,7 @@
         <f>E3</f>
         <v>10</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="20" t="s">
         <v>22</v>
       </c>
       <c r="H3" s="1"/>
@@ -1015,13 +1043,13 @@
         <f t="shared" ref="F4:F8" si="0">E4</f>
         <v>10</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="20" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="23" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="12">
@@ -1040,16 +1068,18 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G5" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="1"/>
+      <c r="G5" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="12">
         <v>2</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -1065,7 +1095,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="1"/>
@@ -1074,7 +1104,7 @@
       <c r="A7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="12">
         <v>1</v>
       </c>
       <c r="C7" s="8">
@@ -1090,7 +1120,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="G7" s="20" t="s">
         <v>22</v>
       </c>
       <c r="H7" s="1"/>
@@ -1115,7 +1145,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="20" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="1"/>
@@ -1124,7 +1154,7 @@
       <c r="A9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="30">
         <v>7</v>
       </c>
       <c r="C9" s="10">
@@ -1140,7 +1170,7 @@
         <f>E9</f>
         <v>8.5</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="19" t="s">
         <v>20</v>
       </c>
       <c r="H9" s="1"/>
@@ -1171,50 +1201,53 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="27">
         <v>20</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="28">
         <v>0.9</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="28">
         <v>0.6</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="28">
         <v>7</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="16">
         <f>E13</f>
         <v>7</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="22" t="s">
         <v>24</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="17">
         <v>15</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="19">
-        <v>10</v>
-      </c>
-      <c r="F14" s="19">
+      <c r="E14" s="18">
+        <v>10</v>
+      </c>
+      <c r="F14" s="18">
         <f>E14</f>
         <v>10</v>
       </c>
-      <c r="G14" s="28" t="s">
+      <c r="G14" s="24" t="s">
         <v>23</v>
       </c>
     </row>
